--- a/Data/C02 Figures.xlsx
+++ b/Data/C02 Figures.xlsx
@@ -24049,6 +24049,15 @@
         <v>2.95</v>
       </c>
     </row>
+    <row r="908">
+      <c r="A908" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B908"/>
+      <c r="C908" t="n">
+        <v>3.14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Data/C02 Figures.xlsx
+++ b/Data/C02 Figures.xlsx
@@ -14060,6 +14060,14 @@
         <v>2.79805352798053</v>
       </c>
     </row>
+    <row r="1340">
+      <c r="A1340" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B1340" t="n">
+        <v>3.03214069132807</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -24053,7 +24061,9 @@
       <c r="A908" s="1" t="n">
         <v>46204</v>
       </c>
-      <c r="B908"/>
+      <c r="B908" t="n">
+        <v>0.711573070937889</v>
+      </c>
       <c r="C908" t="n">
         <v>3.14</v>
       </c>

--- a/Data/C02 Figures.xlsx
+++ b/Data/C02 Figures.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="266">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -800,6 +800,9 @@
   </si>
   <si>
     <t xml:space="preserve">Jan 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apr 2026</t>
   </si>
   <si>
     <t xml:space="preserve">inflation</t>
@@ -3333,7 +3336,15 @@
         <v>261</v>
       </c>
       <c r="B261" t="n">
-        <v>-0.142713715769993</v>
+        <v>0.325151376251309</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="s">
+        <v>262</v>
+      </c>
+      <c r="B262" t="n">
+        <v>3.31949209830804</v>
       </c>
     </row>
   </sheetData>
@@ -3353,7 +3364,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2">
@@ -14085,10 +14096,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2">
@@ -24066,6 +24077,15 @@
       </c>
       <c r="C908" t="n">
         <v>3.14</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B909"/>
+      <c r="C909" t="n">
+        <v>3.21</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C02 Figures.xlsx
+++ b/Data/C02 Figures.xlsx
@@ -14079,6 +14079,14 @@
         <v>3.03214069132807</v>
       </c>
     </row>
+    <row r="1341">
+      <c r="A1341" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B1341" t="n">
+        <v>3.03398058252426</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -24083,7 +24091,9 @@
       <c r="A909" s="1" t="n">
         <v>46235</v>
       </c>
-      <c r="B909"/>
+      <c r="B909" t="n">
+        <v>0.930894842434958</v>
+      </c>
       <c r="C909" t="n">
         <v>3.21</v>
       </c>

--- a/Data/C02 Figures.xlsx
+++ b/Data/C02 Figures.xlsx
@@ -24098,6 +24098,15 @@
         <v>3.21</v>
       </c>
     </row>
+    <row r="910">
+      <c r="A910" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B910"/>
+      <c r="C910" t="n">
+        <v>3.65</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
